--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ARKANSAS_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ARKANSAS_2021.xlsx
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C119">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C186">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C194">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C468">
